--- a/results/qc/gdsc_expression_QC.xlsx
+++ b/results/qc/gdsc_expression_QC.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="215">
   <si>
     <t>Metric</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t>Duplicated cell-line IDs</t>
+  </si>
+  <si>
+    <t>Duplicated glioma cell-line IDs</t>
   </si>
   <si>
     <t>Completely missing expression profiles</t>
@@ -990,7 +993,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1006,7 +1009,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1014,7 +1017,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1062,7 +1065,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1070,7 +1073,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1094,7 +1097,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>2.0651824797739</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1102,6 +1105,14 @@
         <v>14</v>
       </c>
       <c r="B14">
+        <v>2.0651824797739</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15">
         <v>13.9602948479548</v>
       </c>
     </row>
@@ -1117,49 +1128,49 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
         <v>21</v>
-      </c>
-      <c r="B1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2" t="b">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" t="b">
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4" t="b">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D4">
         <v>687588</v>
@@ -1167,13 +1178,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5" t="b">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D5">
         <v>1240150</v>
@@ -1181,13 +1192,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6" t="b">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D6">
         <v>687590</v>
@@ -1195,13 +1206,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7" t="b">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D7">
         <v>906868</v>
@@ -1209,13 +1220,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B8" t="b">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D8">
         <v>906873</v>
@@ -1223,35 +1234,35 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" t="b">
         <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" t="b">
         <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B11" t="b">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D11">
         <v>687562</v>
@@ -1259,24 +1270,24 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12" t="b">
         <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" t="b">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D13">
         <v>908449</v>
@@ -1284,35 +1295,35 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B14" t="b">
         <v>0</v>
       </c>
       <c r="C14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15" t="b">
         <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B16" t="b">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D16">
         <v>907271</v>
@@ -1320,13 +1331,13 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17" t="b">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D17">
         <v>905983</v>
@@ -1334,13 +1345,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" t="b">
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D18">
         <v>906839</v>
@@ -1348,13 +1359,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B19" t="b">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D19">
         <v>910933</v>
@@ -1362,13 +1373,13 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20" t="b">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D20">
         <v>905984</v>
@@ -1376,35 +1387,35 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B21" t="b">
         <v>0</v>
       </c>
       <c r="C21" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B22" t="b">
         <v>0</v>
       </c>
       <c r="C22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B23" t="b">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D23">
         <v>687561</v>
@@ -1412,24 +1423,24 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B24" t="b">
         <v>0</v>
       </c>
       <c r="C24" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B25" t="b">
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D25">
         <v>906823</v>
@@ -1437,35 +1448,35 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B26" t="b">
         <v>0</v>
       </c>
       <c r="C26" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B27" t="b">
         <v>0</v>
       </c>
       <c r="C27" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B28" t="b">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D28">
         <v>905985</v>
@@ -1473,13 +1484,13 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B29" t="b">
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D29">
         <v>907042</v>
@@ -1487,13 +1498,13 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B30" t="b">
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D30">
         <v>909745</v>
@@ -1501,35 +1512,35 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B31" t="b">
         <v>0</v>
       </c>
       <c r="C31" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B32" t="b">
         <v>0</v>
       </c>
       <c r="C32" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B33" t="b">
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D33">
         <v>910943</v>
@@ -1537,13 +1548,13 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B34" t="b">
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D34">
         <v>909905</v>
@@ -1551,24 +1562,24 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B35" t="b">
         <v>0</v>
       </c>
       <c r="C35" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B36" t="b">
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D36">
         <v>905982</v>
@@ -1576,24 +1587,24 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B37" t="b">
         <v>0</v>
       </c>
       <c r="C37" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B38" t="b">
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D38">
         <v>687563</v>
@@ -1601,13 +1612,13 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B39" t="b">
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D39">
         <v>687592</v>
@@ -1615,13 +1626,13 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B40" t="b">
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D40">
         <v>687586</v>
@@ -1629,35 +1640,35 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B41" t="b">
         <v>0</v>
       </c>
       <c r="C41" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B42" t="b">
         <v>0</v>
       </c>
       <c r="C42" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B43" t="b">
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D43">
         <v>1240169</v>
@@ -1665,13 +1676,13 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B44" t="b">
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D44">
         <v>909712</v>
@@ -1679,13 +1690,13 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B45" t="b">
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D45">
         <v>907282</v>
@@ -1693,24 +1704,24 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B46" t="b">
         <v>0</v>
       </c>
       <c r="C46" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B47" t="b">
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D47">
         <v>907313</v>
@@ -1718,24 +1729,24 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B48" t="b">
         <v>0</v>
       </c>
       <c r="C48" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B49" t="b">
         <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D49">
         <v>905986</v>
@@ -1743,24 +1754,24 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B50" t="b">
         <v>0</v>
       </c>
       <c r="C50" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B51" t="b">
         <v>1</v>
       </c>
       <c r="C51" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D51">
         <v>687568</v>
@@ -1768,13 +1779,13 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B52" t="b">
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D52">
         <v>906871</v>
@@ -1782,35 +1793,35 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B53" t="b">
         <v>0</v>
       </c>
       <c r="C53" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B54" t="b">
         <v>0</v>
       </c>
       <c r="C54" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B55" t="b">
         <v>1</v>
       </c>
       <c r="C55" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D55">
         <v>1240168</v>
@@ -1818,13 +1829,13 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B56" t="b">
         <v>1</v>
       </c>
       <c r="C56" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D56">
         <v>906835</v>
@@ -1832,13 +1843,13 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B57" t="b">
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D57">
         <v>909750</v>
@@ -1846,35 +1857,35 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B58" t="b">
         <v>0</v>
       </c>
       <c r="C58" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B59" t="b">
         <v>0</v>
       </c>
       <c r="C59" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B60" t="b">
         <v>1</v>
       </c>
       <c r="C60" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D60">
         <v>906746</v>
@@ -1882,13 +1893,13 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B61" t="b">
         <v>1</v>
       </c>
       <c r="C61" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D61">
         <v>949094</v>
@@ -1896,13 +1907,13 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B62" t="b">
         <v>1</v>
       </c>
       <c r="C62" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D62">
         <v>908144</v>
@@ -1910,13 +1921,13 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B63" t="b">
         <v>1</v>
       </c>
       <c r="C63" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D63">
         <v>908145</v>
@@ -1924,57 +1935,57 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B64" t="b">
         <v>0</v>
       </c>
       <c r="C64" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B65" t="b">
         <v>0</v>
       </c>
       <c r="C65" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B66" t="b">
         <v>0</v>
       </c>
       <c r="C66" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B67" t="b">
         <v>0</v>
       </c>
       <c r="C67" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B68" t="b">
         <v>1</v>
       </c>
       <c r="C68" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D68">
         <v>908452</v>
@@ -1982,13 +1993,13 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B69" t="b">
         <v>1</v>
       </c>
       <c r="C69" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D69">
         <v>908450</v>
@@ -1996,90 +2007,90 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B70" t="b">
         <v>0</v>
       </c>
       <c r="C70" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B71" t="b">
         <v>0</v>
       </c>
       <c r="C71" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B72" t="b">
         <v>0</v>
       </c>
       <c r="C72" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B73" t="b">
         <v>0</v>
       </c>
       <c r="C73" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B74" t="b">
         <v>0</v>
       </c>
       <c r="C74" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B75" t="b">
         <v>0</v>
       </c>
       <c r="C75" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B76" t="b">
         <v>0</v>
       </c>
       <c r="C76" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B77" t="b">
         <v>0</v>
       </c>
       <c r="C77" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D77">
         <v>946366</v>
@@ -2087,13 +2098,13 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B78" t="b">
         <v>1</v>
       </c>
       <c r="C78" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D78">
         <v>946367</v>
@@ -2101,13 +2112,13 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B79" t="b">
         <v>1</v>
       </c>
       <c r="C79" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D79">
         <v>946368</v>
@@ -2115,13 +2126,13 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B80" t="b">
         <v>1</v>
       </c>
       <c r="C80" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D80">
         <v>946369</v>
@@ -2129,13 +2140,13 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B81" t="b">
         <v>1</v>
       </c>
       <c r="C81" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D81">
         <v>946370</v>
@@ -2143,13 +2154,13 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B82" t="b">
         <v>1</v>
       </c>
       <c r="C82" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D82">
         <v>946372</v>
@@ -2157,13 +2168,13 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B83" t="b">
         <v>1</v>
       </c>
       <c r="C83" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D83">
         <v>946373</v>
@@ -2171,13 +2182,13 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B84" t="b">
         <v>1</v>
       </c>
       <c r="C84" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D84">
         <v>753549</v>
@@ -2185,13 +2196,13 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B85" t="b">
         <v>1</v>
       </c>
       <c r="C85" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D85">
         <v>946377</v>
@@ -2199,13 +2210,13 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B86" t="b">
         <v>1</v>
       </c>
       <c r="C86" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D86">
         <v>907279</v>
@@ -2213,13 +2224,13 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B87" t="b">
         <v>1</v>
       </c>
       <c r="C87" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D87">
         <v>924188</v>
@@ -2227,13 +2238,13 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B88" t="b">
         <v>1</v>
       </c>
       <c r="C88" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D88">
         <v>910694</v>
@@ -2241,13 +2252,13 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B89" t="b">
         <v>1</v>
       </c>
       <c r="C89" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D89">
         <v>1240170</v>
@@ -2255,13 +2266,13 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B90" t="b">
         <v>1</v>
       </c>
       <c r="C90" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D90">
         <v>909729</v>
@@ -2269,79 +2280,79 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B91" t="b">
         <v>0</v>
       </c>
       <c r="C91" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B92" t="b">
         <v>0</v>
       </c>
       <c r="C92" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B93" t="b">
         <v>0</v>
       </c>
       <c r="C93" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B94" t="b">
         <v>0</v>
       </c>
       <c r="C94" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B95" t="b">
         <v>0</v>
       </c>
       <c r="C95" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B96" t="b">
         <v>0</v>
       </c>
       <c r="C96" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B97" t="b">
         <v>0</v>
       </c>
       <c r="C97" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -2356,227 +2367,227 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -2591,7 +2602,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
